--- a/data/productInfo.xlsx
+++ b/data/productInfo.xlsx
@@ -40,13 +40,13 @@
     <t>food</t>
   </si>
   <si>
-    <t>Donut</t>
-  </si>
-  <si>
     <t>red red</t>
   </si>
   <si>
     <t>Pepsi</t>
+  </si>
+  <si>
+    <t>chicken burger</t>
   </si>
 </sst>
 </file>
@@ -409,10 +409,10 @@
         <v>1.5</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -423,7 +423,7 @@
         <v>1.5</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
@@ -434,13 +434,13 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/productInfo.xlsx
+++ b/data/productInfo.xlsx
@@ -437,7 +437,7 @@
         <v>2.5</v>
       </c>
       <c r="C6">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
